--- a/5/search/FY3_Missile3_results/solutions_direction_81.0.xlsx
+++ b/5/search/FY3_Missile3_results/solutions_direction_81.0.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,34 +490,34 @@
         <v>81</v>
       </c>
       <c r="B2" t="n">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C2" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>6420.495842028141</v>
+        <v>6446.776832154899</v>
       </c>
       <c r="F2" t="n">
-        <v>-345.0937404802698</v>
+        <v>-179.1620992602866</v>
       </c>
       <c r="G2" t="n">
         <v>700</v>
       </c>
       <c r="H2" t="n">
-        <v>6446.7768321549</v>
+        <v>6446.776832154899</v>
       </c>
       <c r="I2" t="n">
-        <v>-179.1620992602867</v>
+        <v>-179.1620992602866</v>
       </c>
       <c r="J2" t="n">
-        <v>680.4</v>
+        <v>700</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -525,34 +525,34 @@
         <v>81</v>
       </c>
       <c r="B3" t="n">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>6429.256172070393</v>
+        <v>6450.531259315865</v>
       </c>
       <c r="F3" t="n">
-        <v>-289.7831934069422</v>
+        <v>-155.4575790860035</v>
       </c>
       <c r="G3" t="n">
         <v>700</v>
       </c>
       <c r="H3" t="n">
-        <v>6444.586749644336</v>
+        <v>6450.531259315865</v>
       </c>
       <c r="I3" t="n">
-        <v>-192.9897360286188</v>
+        <v>-155.4575790860035</v>
       </c>
       <c r="J3" t="n">
-        <v>695.1</v>
+        <v>700</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -560,68 +560,33 @@
         <v>81</v>
       </c>
       <c r="B4" t="n">
-        <v>114.8</v>
+        <v>138</v>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>6431.008238078844</v>
+        <v>6431.759123511038</v>
       </c>
       <c r="F4" t="n">
-        <v>-278.7210839922764</v>
+        <v>-273.9801799574198</v>
       </c>
       <c r="G4" t="n">
         <v>700</v>
       </c>
       <c r="H4" t="n">
-        <v>6448.966914665463</v>
+        <v>6453.347079686589</v>
       </c>
       <c r="I4" t="n">
-        <v>-165.3344624919546</v>
+        <v>-137.6791889552907</v>
       </c>
       <c r="J4" t="n">
         <v>695.1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>81</v>
-      </c>
-      <c r="B5" t="n">
-        <v>120.4</v>
-      </c>
-      <c r="C5" t="n">
-        <v>24</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>6452.033030180251</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-145.9757710162899</v>
-      </c>
-      <c r="G5" t="n">
-        <v>700</v>
-      </c>
-      <c r="H5" t="n">
-        <v>6452.033030180251</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-145.9757710162899</v>
-      </c>
-      <c r="J5" t="n">
-        <v>700</v>
-      </c>
-      <c r="K5" t="n">
         <v>3</v>
       </c>
     </row>
